--- a/tiflow-rx/build/1.0.0-draft/StructureDefinition-GEM-ERP-EX-AvailabilityState.xlsx
+++ b/tiflow-rx/build/1.0.0-draft/StructureDefinition-GEM-ERP-EX-AvailabilityState.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="152">
   <si>
     <t>Property</t>
   </si>
@@ -447,9 +447,6 @@
   </si>
   <si>
     <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
@@ -1459,7 +1456,7 @@
         <v>85</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>110</v>
@@ -2029,11 +2026,9 @@
       <c r="M12" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="N12" t="s" s="2">
+      <c r="N12" s="2"/>
+      <c r="O12" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2082,7 +2077,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2097,15 +2092,15 @@
         <v>110</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2128,19 +2123,19 @@
         <v>118</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="N13" t="s" s="2">
+      <c r="O13" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>150</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -2189,7 +2184,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2204,7 +2199,7 @@
         <v>110</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
